--- a/output/pdf_financials_xlsx/NUG.xlsx
+++ b/output/pdf_financials_xlsx/NUG.xlsx
@@ -6242,40 +6242,40 @@
         <v>0</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0</v>
+        <v>-0.574308</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>-1.646238</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0</v>
+        <v>-3.196298</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0</v>
+        <v>-2.972169</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0</v>
+        <v>-2.957287</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>0</v>
+        <v>-3.216548</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>0</v>
+        <v>-3.205395</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>0</v>
+        <v>-3.211806</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>0</v>
+        <v>-3.264627</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>0</v>
+        <v>-3.294622</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>0</v>
+        <v>-3.295738</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>0</v>
+        <v>-3.295738</v>
       </c>
     </row>
     <row r="92">
@@ -6294,49 +6294,49 @@
         <v>0</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0.419333</v>
+        <v>1.233547</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.51888</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.927108</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>3.73403</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>3.73403</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>4.011622</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>6.343292</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>6.337122</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>6.941973</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>8.704851</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>14.670145</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>14.670145</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>14.670145</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>15.274482</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>15.917282</v>
       </c>
     </row>
     <row r="93">
@@ -7836,43 +7836,43 @@
         <v>-2.326921</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0.014</v>
+        <v>-2.059319</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0.012</v>
+        <v>-0.684053</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0.01</v>
+        <v>-1.88435</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>4.16</v>
+        <v>2.363286</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-4.219625</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-5.743005</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-5.225932</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-2.517881</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-4.490437</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-8.286282999999999</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0</v>
+        <v>-2.016493</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>0</v>
+        <v>-1.650241</v>
       </c>
       <c r="S118" s="3" t="n">
-        <v>46.72284</v>
+        <v>46.230824</v>
       </c>
     </row>
     <row r="119">
@@ -10326,7 +10326,11 @@
           <t>Warrants reserve 9</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -10522,7 +10526,11 @@
           <t>Revaluation reserve</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -11634,7 +11642,11 @@
           <t>Warrants reserve 9</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -11830,7 +11842,11 @@
           <t>Revaluation reserve</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -13550,7 +13566,11 @@
           <t>Warrants reserve 9</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -13750,7 +13770,11 @@
           <t>Revaluation reserve</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -14268,7 +14292,11 @@
           <t>Revaluation reserve 3</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -14794,7 +14822,11 @@
           <t>Revaluation reserve 4</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -15956,7 +15988,11 @@
           <t>Warrants reserve 10</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -16164,7 +16200,11 @@
           <t>Revaluation reserve 5</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -17016,7 +17056,11 @@
           <t>Warrants reserve 10</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
@@ -18184,7 +18228,11 @@
           <t>Warrants reserve 11</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -22302,7 +22350,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
@@ -28628,7 +28680,11 @@
           <t>Exploration and evaluation asset expenditures $</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>
@@ -30950,7 +31006,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NUG.xlsx
+++ b/output/pdf_financials_xlsx/NUG.xlsx
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000182</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.009320999999999999</v>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
@@ -1101,34 +1101,34 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.001163</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.06775</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.087492</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.051315</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.000422</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>7.6e-05</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.00012</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.000241</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.008396000000000001</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>0.001404</v>
       </c>
     </row>
     <row r="13">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.22916</v>
+        <v>-1.229342</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.635532</v>
+        <v>-0.644853</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
@@ -2204,34 +2204,34 @@
         <v>-1.325258</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1.697267</v>
+        <v>-1.69843</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-3.015302</v>
+        <v>-3.083052</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-4.055847</v>
+        <v>-4.143339</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-3.228868</v>
+        <v>-3.280183</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-1.814102</v>
+        <v>-1.814524</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-3.403288</v>
+        <v>-3.403364</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-2.568583</v>
+        <v>-2.568703</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-1.492806</v>
+        <v>-1.493047</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-1.459324</v>
+        <v>-1.46772</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-47.284229</v>
+        <v>-47.285633</v>
       </c>
     </row>
     <row r="28">
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.22916</v>
+        <v>-1.229342</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.635532</v>
+        <v>-0.644853</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -2330,34 +2330,34 @@
         <v>-1.318314</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-1.685346</v>
+        <v>-1.686509</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-2.977337</v>
+        <v>-3.045087</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-3.95999</v>
+        <v>-4.047482</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-3.123229</v>
+        <v>-3.174544</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-1.739497</v>
+        <v>-1.739919</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-3.321336</v>
+        <v>-3.321412</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-2.442078</v>
+        <v>-2.442198</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-1.421092</v>
+        <v>-1.421333</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-1.413847</v>
+        <v>-1.422243</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-47.275323</v>
+        <v>-47.276727</v>
       </c>
     </row>
     <row r="30">
@@ -2670,19 +2670,19 @@
         <v>5.25154</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>15.675502</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>5.174535</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>1.977196</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.19971</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.105969</v>
       </c>
     </row>
     <row r="35">
@@ -2792,19 +2792,19 @@
         <v>5.25154</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>15.675502</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>5.174535</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>1.977196</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.19971</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>0.105969</v>
       </c>
     </row>
     <row r="37">
@@ -3524,19 +3524,19 @@
         <v>0.170121</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>15.829101</v>
+        <v>0.153599</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>5.270944</v>
+        <v>0.09640899999999999</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>2.081287</v>
+        <v>0.104091</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.252902</v>
+        <v>0.053192</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>0.128819</v>
+        <v>0.02285</v>
       </c>
     </row>
     <row r="49">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -20254,7 +20254,11 @@
           <t>Reclamation Deposits (Note 3)</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E110" s="5" t="n">
         <v>0.005045</v>
       </c>
@@ -40464,7 +40468,11 @@
           <t>Accrued interest on reclamation deposits</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E304" s="5" t="n">
         <v>2.5e-05</v>
       </c>
@@ -40568,7 +40576,11 @@
           <t>Recovery of reclamation deposit</t>
         </is>
       </c>
-      <c r="D305" t="inlineStr"/>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E305" s="5" t="n">
         <v>0.002</v>
       </c>
@@ -43904,7 +43916,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -47212,7 +47224,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -58232,7 +58244,7 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E475" s="5" t="n">

--- a/output/pdf_financials_xlsx/NUG.xlsx
+++ b/output/pdf_financials_xlsx/NUG.xlsx
@@ -763,7 +763,7 @@
         <v>0.138758</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.130636</v>
+        <v>0.135636</v>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
@@ -792,28 +792,28 @@
         <v>0.8647049999999999</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>1.007897</v>
+        <v>1.097902</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.136774</v>
+        <v>1.216774</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.78329</v>
+        <v>0.7982900000000001</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1.086047</v>
+        <v>1.146047</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>1.019374</v>
+        <v>1.064206</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.9096109999999999</v>
+        <v>0.936111</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>1.003791</v>
+        <v>1.031973</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.289857</v>
+        <v>0.301107</v>
       </c>
     </row>
     <row r="8">
@@ -1353,7 +1353,7 @@
         <v>-1.325258</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-1.697267</v>
+        <v>-1.646672</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>-3.015302</v>
@@ -1390,10 +1390,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.093</v>
+        <v>-0.093</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0.027865</v>
+        <v>0.027865</v>
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>-0</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.050595</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>-0</v>
@@ -2204,7 +2204,7 @@
         <v>-1.325258</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1.69843</v>
+        <v>-1.647835</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-3.083052</v>
@@ -2330,7 +2330,7 @@
         <v>-1.318314</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-1.686509</v>
+        <v>-1.635914</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-3.045087</v>
@@ -2490,7 +2490,7 @@
         <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-0</v>
+        <v>-3.072560898588183</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>-0</v>
@@ -7403,22 +7403,22 @@
         <v>0</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.004185</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.015122</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.010675</v>
       </c>
       <c r="H111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.019891</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.015887</v>
       </c>
       <c r="K111" s="3" t="n">
         <v>0</v>
@@ -8026,7 +8026,7 @@
         <v>0</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="E121" s="3" t="n">
         <v>0</v>
@@ -8874,22 +8874,22 @@
         <v>0</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.004185</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.015122</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.010675</v>
       </c>
       <c r="H134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.019891</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.015887</v>
       </c>
       <c r="K134" s="3" t="n">
         <v>0</v>
@@ -8937,13 +8937,13 @@
         </is>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-0.739904</v>
+        <v>-0.744089</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-0.971108</v>
+        <v>-0.9862300000000001</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-1.341975</v>
+        <v>-1.35265</v>
       </c>
       <c r="H135" s="1" t="inlineStr">
         <is>
@@ -26762,7 +26762,11 @@
           <t>Warrants issued in private placement $</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
@@ -29616,7 +29620,11 @@
           <t>Warrants issued in private placement</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -32942,7 +32950,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -38558,7 +38570,11 @@
           <t>Excess paid for repurchase of shares</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr"/>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E286" t="inlineStr">
         <is>
           <t>-</t>
@@ -38872,7 +38888,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr"/>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E289" t="inlineStr">
         <is>
           <t>-</t>
@@ -40794,7 +40814,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr"/>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E307" s="5" t="n">
         <v>0.4582</v>
       </c>
@@ -42696,7 +42720,11 @@
           <t>Directors’ fees 8</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr"/>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E325" t="inlineStr">
         <is>
           <t>-</t>
@@ -46080,7 +46108,11 @@
           <t>Directors' fees</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr"/>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E358" t="inlineStr">
         <is>
           <t>-</t>
@@ -48960,7 +48992,11 @@
           <t>Income tax recovery 13</t>
         </is>
       </c>
-      <c r="D387" t="inlineStr"/>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E387" t="inlineStr">
         <is>
           <t>-</t>
@@ -57064,7 +57100,11 @@
           <t>Directors fees</t>
         </is>
       </c>
-      <c r="D464" t="inlineStr"/>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E464" t="inlineStr">
         <is>
           <t>-</t>
@@ -58564,7 +58604,11 @@
           <t>Future income tax recovery (expense) (Note 8)</t>
         </is>
       </c>
-      <c r="D478" t="inlineStr"/>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E478" s="5" t="n">
         <v>0.093</v>
       </c>
